--- a/results_v3/tables/table7_computational_cost.xlsx
+++ b/results_v3/tables/table7_computational_cost.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,44 +527,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>POMCP (known model)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DQN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>572</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,34 +574,115 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DQN-GRU (memory)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPO-Stack (memory)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>MuZero (ours)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>11131</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11114</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>6.75</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1000000</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2000000</t>
         </is>
       </c>
     </row>
